--- a/Mixed Referencing.xlsx
+++ b/Mixed Referencing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1107432E-2CED-4E67-BE33-343243A58584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C71EFFD-61A5-4CD5-8F4F-7347EDD85A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{177AFE0A-2CFE-4EF0-A57D-D737CF250A3A}"/>
   </bookViews>
@@ -33,10 +33,26 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>*=B$1*$A2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -64,8 +80,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,8 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2A18211-60E4-49C9-BCEB-CED85C31316A}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1">
@@ -424,7 +444,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:J10" si="0">C$1*$A2</f>
+        <f t="shared" ref="C2:J2" si="0">C$1*$A2</f>
         <v>6</v>
       </c>
       <c r="D2">
@@ -465,35 +485,35 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C2:J10" si="2">C$1*$A3</f>
         <v>9</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="E3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="H3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -506,35 +526,35 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
     </row>
@@ -547,35 +567,35 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
     </row>
@@ -588,35 +608,35 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
     </row>
@@ -629,35 +649,35 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="D7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="H7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
     </row>
@@ -670,35 +690,35 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="G8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
     </row>
@@ -711,35 +731,35 @@
         <v>18</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="D9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="H9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
     </row>
@@ -752,36 +772,41 @@
         <v>20</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="D10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="H10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C13" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
